--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ70"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -930,76 +930,64 @@
       <c r="AK3" t="inlineStr">
         <is>
           <t>6.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Árbitro 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RADOVIC, SRETEN (Croatia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Árbitro 2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>KOLJENSIC, MILOS  (Montenegro)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Árbitro 3</t>
+          <t>Árbitro 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RACYS, SAULIUS (Sweden)</t>
+          <t>RADOVIC, SRETEN (Croatia)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pabellón</t>
+          <t>Árbitro 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KOLJENSIC, MILOS  (Montenegro)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lugar</t>
+          <t>Árbitro 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RACYS, SAULIUS (Sweden)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Asistencia</t>
+          <t>Pabellón</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lugar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1008,880 +996,304 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LDLC ASVEL VILLEURBANNE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>JUGADOR</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>2PM</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>2PA</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>3PM</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>3PA</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>FTM</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>FTA</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>DRB</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>ORB</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>BLK A.</t>
-        </is>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>TOunf</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R13" s="1" t="inlineStr">
-        <is>
-          <t>F+</t>
-        </is>
-      </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="T13" s="1" t="inlineStr">
-        <is>
-          <t>TOpts</t>
-        </is>
-      </c>
-      <c r="U13" s="1" t="inlineStr">
-        <is>
-          <t>2CPts</t>
-        </is>
-      </c>
-      <c r="V13" s="1" t="inlineStr">
-        <is>
-          <t>FastBPts</t>
-        </is>
-      </c>
-      <c r="W13" s="1" t="inlineStr">
-        <is>
-          <t>FastB Opp</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>Rim FGM</t>
-        </is>
-      </c>
-      <c r="Y13" s="1" t="inlineStr">
-        <is>
-          <t>Rim FGA</t>
-        </is>
-      </c>
-      <c r="Z13" s="1" t="inlineStr">
-        <is>
-          <t>Rim %</t>
-        </is>
-      </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>Paint FGM</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>Paint FGA</t>
-        </is>
-      </c>
-      <c r="AC13" s="1" t="inlineStr">
-        <is>
-          <t>Paint %</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>MR FGM</t>
-        </is>
-      </c>
-      <c r="AE13" s="1" t="inlineStr">
-        <is>
-          <t>MR FGA</t>
-        </is>
-      </c>
-      <c r="AF13" s="1" t="inlineStr">
-        <is>
-          <t>MR %</t>
-        </is>
-      </c>
-      <c r="AG13" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 FGM</t>
-        </is>
-      </c>
-      <c r="AH13" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 FGA</t>
-        </is>
-      </c>
-      <c r="AI13" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 %</t>
-        </is>
-      </c>
-      <c r="AJ13" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 FGM</t>
-        </is>
-      </c>
-      <c r="AK13" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 FGA</t>
-        </is>
-      </c>
-      <c r="AL13" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 %</t>
-        </is>
-      </c>
-      <c r="AM13" s="1" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="AN13" s="1" t="inlineStr">
-        <is>
-          <t>PLAYS</t>
-        </is>
-      </c>
-      <c r="AO13" s="1" t="inlineStr">
-        <is>
-          <t>eFG%</t>
-        </is>
-      </c>
-      <c r="AP13" s="1" t="inlineStr">
-        <is>
-          <t>TS%</t>
-        </is>
-      </c>
-      <c r="AQ13" s="1" t="inlineStr">
-        <is>
-          <t>PTS/PLAY</t>
-        </is>
-      </c>
-      <c r="AR13" s="1" t="inlineStr">
-        <is>
-          <t>TO%</t>
-        </is>
-      </c>
-      <c r="AS13" s="1" t="inlineStr">
-        <is>
-          <t>FTR</t>
-        </is>
-      </c>
-      <c r="AT13" s="1" t="inlineStr">
-        <is>
-          <t>Ass/TO</t>
-        </is>
-      </c>
-      <c r="AU13" s="1" t="inlineStr">
-        <is>
-          <t>Sh/TO</t>
-        </is>
-      </c>
-      <c r="AV13" s="1" t="inlineStr">
-        <is>
-          <t>Gen/TO</t>
-        </is>
-      </c>
-      <c r="AW13" s="1" t="inlineStr">
-        <is>
-          <t>USG%</t>
-        </is>
-      </c>
-      <c r="AX13" s="1" t="inlineStr">
-        <is>
-          <t>OR%</t>
-        </is>
-      </c>
-      <c r="AY13" s="1" t="inlineStr">
-        <is>
-          <t>DR%</t>
-        </is>
-      </c>
-      <c r="AZ13" s="1" t="inlineStr">
-        <is>
-          <t>pAST%</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>#1 Z. SELJAAS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>15</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>56:12</t>
-        </is>
-      </c>
-      <c r="AN14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>45.0%</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>45.0%</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>8.5%</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5.5%</t>
+          <t>Asistencia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>#2 A. ATAMNA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+          <t>LDLC ASVEL VILLEURBANNE</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>#3 S. HARRISON</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>53:17</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>8.9%</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5.8%</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>JUGADOR</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>2PM</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>2PA</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>3PM</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>3PA</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>FTM</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>FTA</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>DRB</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>BLK A.</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>TOunf</t>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>F+</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="T16" s="1" t="inlineStr">
+        <is>
+          <t>TOpts</t>
+        </is>
+      </c>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t>2CPts</t>
+        </is>
+      </c>
+      <c r="V16" s="1" t="inlineStr">
+        <is>
+          <t>FastBPts</t>
+        </is>
+      </c>
+      <c r="W16" s="1" t="inlineStr">
+        <is>
+          <t>FastB Opp</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="inlineStr">
+        <is>
+          <t>Rim FGM</t>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t>Rim FGA</t>
+        </is>
+      </c>
+      <c r="Z16" s="1" t="inlineStr">
+        <is>
+          <t>Rim %</t>
+        </is>
+      </c>
+      <c r="AA16" s="1" t="inlineStr">
+        <is>
+          <t>Paint FGM</t>
+        </is>
+      </c>
+      <c r="AB16" s="1" t="inlineStr">
+        <is>
+          <t>Paint FGA</t>
+        </is>
+      </c>
+      <c r="AC16" s="1" t="inlineStr">
+        <is>
+          <t>Paint %</t>
+        </is>
+      </c>
+      <c r="AD16" s="1" t="inlineStr">
+        <is>
+          <t>MR FGM</t>
+        </is>
+      </c>
+      <c r="AE16" s="1" t="inlineStr">
+        <is>
+          <t>MR FGA</t>
+        </is>
+      </c>
+      <c r="AF16" s="1" t="inlineStr">
+        <is>
+          <t>MR %</t>
+        </is>
+      </c>
+      <c r="AG16" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 FGM</t>
+        </is>
+      </c>
+      <c r="AH16" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 FGA</t>
+        </is>
+      </c>
+      <c r="AI16" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 %</t>
+        </is>
+      </c>
+      <c r="AJ16" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 FGM</t>
+        </is>
+      </c>
+      <c r="AK16" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 FGA</t>
+        </is>
+      </c>
+      <c r="AL16" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 %</t>
+        </is>
+      </c>
+      <c r="AM16" s="1" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="AN16" s="1" t="inlineStr">
+        <is>
+          <t>PLAYS</t>
+        </is>
+      </c>
+      <c r="AO16" s="1" t="inlineStr">
+        <is>
+          <t>eFG%</t>
+        </is>
+      </c>
+      <c r="AP16" s="1" t="inlineStr">
+        <is>
+          <t>TS%</t>
+        </is>
+      </c>
+      <c r="AQ16" s="1" t="inlineStr">
+        <is>
+          <t>PTS/PLAY</t>
+        </is>
+      </c>
+      <c r="AR16" s="1" t="inlineStr">
+        <is>
+          <t>TO%</t>
+        </is>
+      </c>
+      <c r="AS16" s="1" t="inlineStr">
+        <is>
+          <t>FTR</t>
+        </is>
+      </c>
+      <c r="AT16" s="1" t="inlineStr">
+        <is>
+          <t>Ass/TO</t>
+        </is>
+      </c>
+      <c r="AU16" s="1" t="inlineStr">
+        <is>
+          <t>Sh/TO</t>
+        </is>
+      </c>
+      <c r="AV16" s="1" t="inlineStr">
+        <is>
+          <t>Gen/TO</t>
+        </is>
+      </c>
+      <c r="AW16" s="1" t="inlineStr">
+        <is>
+          <t>USG%</t>
+        </is>
+      </c>
+      <c r="AX16" s="1" t="inlineStr">
+        <is>
+          <t>OR%</t>
+        </is>
+      </c>
+      <c r="AY16" s="1" t="inlineStr">
+        <is>
+          <t>DR%</t>
+        </is>
+      </c>
+      <c r="AZ16" s="1" t="inlineStr">
+        <is>
+          <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>#8 M. AJINCA</t>
+          <t>#1 Z. SELJAAS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1890,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1902,25 +1314,25 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1935,21 +1347,21 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -1960,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -1979,42 +1391,42 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47:11</t>
+          <t>26:28</t>
         </is>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -2029,17 +1441,17 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2049,29 +1461,29 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>#10 B. MASSA</t>
+          <t>#2 A. ATAMNA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2089,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2104,19 +1516,19 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2142,14 +1554,14 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD18" t="n">
@@ -2187,30 +1599,30 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -2225,17 +1637,17 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2245,7 +1657,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -2257,29 +1669,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>#11 E. JACKSON</t>
+          <t>#3 S. HARRISON</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
@@ -2288,31 +1700,31 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2330,22 +1742,22 @@
         <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AD19" t="n">
@@ -2363,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -2383,111 +1795,111 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>34:22</t>
+          <t>23:18</t>
         </is>
       </c>
       <c r="AN19" t="n">
-        <v>2.88</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>#12 N. DE COLO</t>
+          <t>#8 M. AJINCA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2496,22 +1908,22 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>-6</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2523,32 +1935,32 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -2567,67 +1979,67 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>43:49</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AN20" t="n">
-        <v>14.88</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2637,50 +2049,50 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>#23 D. LIGHTY</t>
+          <t>#10 B. MASSA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2692,25 +2104,25 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2719,27 +2131,27 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
@@ -2763,42 +2175,42 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>30:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -2813,100 +2225,100 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>#24 M. NDIAYE</t>
+          <t>#11 E. JACKSON</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2915,93 +2327,93 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>34.7%</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>39:50</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>77.3%</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -3019,203 +2431,203 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>#30 G. WATSON</t>
+          <t>#12 N. DE COLO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3</v>
       </c>
       <c r="Y23" t="n">
         <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>3</v>
       </c>
-      <c r="AB23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1</v>
-      </c>
       <c r="AK23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>39:06</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AN23" t="n">
-        <v>13.76</v>
+        <v>14.88</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3225,92 +2637,92 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>#32 B. VAUTIER</t>
+          <t>#23 D. LIGHTY</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
         <v>4</v>
       </c>
-      <c r="D24" t="n">
-        <v>5</v>
-      </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>15</v>
-      </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3318,80 +2730,80 @@
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>2</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>29:07</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AN24" t="n">
-        <v>8.640000000000001</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
@@ -3401,76 +2813,76 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>#94 A. TRAORE</t>
+          <t>#24 M. NDIAYE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3482,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3503,25 +2915,25 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AD25" t="n">
@@ -3550,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
@@ -3559,195 +2971,251 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>3.88</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AU25" t="inlineStr">
+      <c r="AV25" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>#30 G. WATSON</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>12</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4</v>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>3</v>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>4</v>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
       <c r="AI26" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>4</v>
+      </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.76</v>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AU26" t="inlineStr">
+      <c r="AV26" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3757,103 +3225,103 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>#32 B. VAUTIER</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Y27" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -3861,21 +3329,21 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3883,962 +3351,906 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AN27" t="n">
-        <v>84.04000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>#94 A. TRAORE</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>14.4%</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VALENCIA BASKET</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>JUGADOR</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>2PM</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>2PA</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>3PM</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>3PA</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>FTM</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>FTA</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>DRB</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>ORB</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="M31" s="1" t="inlineStr">
-        <is>
-          <t>BLK</t>
-        </is>
-      </c>
-      <c r="N31" s="1" t="inlineStr">
-        <is>
-          <t>BLK A.</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t>TOunf</t>
-        </is>
-      </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="R31" s="1" t="inlineStr">
-        <is>
-          <t>F+</t>
-        </is>
-      </c>
-      <c r="S31" s="1" t="inlineStr">
-        <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="T31" s="1" t="inlineStr">
-        <is>
-          <t>TOpts</t>
-        </is>
-      </c>
-      <c r="U31" s="1" t="inlineStr">
-        <is>
-          <t>2CPts</t>
-        </is>
-      </c>
-      <c r="V31" s="1" t="inlineStr">
-        <is>
-          <t>FastBPts</t>
-        </is>
-      </c>
-      <c r="W31" s="1" t="inlineStr">
-        <is>
-          <t>FastB Opp</t>
-        </is>
-      </c>
-      <c r="X31" s="1" t="inlineStr">
-        <is>
-          <t>Rim FGM</t>
-        </is>
-      </c>
-      <c r="Y31" s="1" t="inlineStr">
-        <is>
-          <t>Rim FGA</t>
-        </is>
-      </c>
-      <c r="Z31" s="1" t="inlineStr">
-        <is>
-          <t>Rim %</t>
-        </is>
-      </c>
-      <c r="AA31" s="1" t="inlineStr">
-        <is>
-          <t>Paint FGM</t>
-        </is>
-      </c>
-      <c r="AB31" s="1" t="inlineStr">
-        <is>
-          <t>Paint FGA</t>
-        </is>
-      </c>
-      <c r="AC31" s="1" t="inlineStr">
-        <is>
-          <t>Paint %</t>
-        </is>
-      </c>
-      <c r="AD31" s="1" t="inlineStr">
-        <is>
-          <t>MR FGM</t>
-        </is>
-      </c>
-      <c r="AE31" s="1" t="inlineStr">
-        <is>
-          <t>MR FGA</t>
-        </is>
-      </c>
-      <c r="AF31" s="1" t="inlineStr">
-        <is>
-          <t>MR %</t>
-        </is>
-      </c>
-      <c r="AG31" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 FGM</t>
-        </is>
-      </c>
-      <c r="AH31" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 FGA</t>
-        </is>
-      </c>
-      <c r="AI31" s="1" t="inlineStr">
-        <is>
-          <t>Cor3 %</t>
-        </is>
-      </c>
-      <c r="AJ31" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 FGM</t>
-        </is>
-      </c>
-      <c r="AK31" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 FGA</t>
-        </is>
-      </c>
-      <c r="AL31" s="1" t="inlineStr">
-        <is>
-          <t>ATB3 %</t>
-        </is>
-      </c>
-      <c r="AM31" s="1" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
-      <c r="AN31" s="1" t="inlineStr">
-        <is>
-          <t>PLAYS</t>
-        </is>
-      </c>
-      <c r="AO31" s="1" t="inlineStr">
-        <is>
-          <t>eFG%</t>
-        </is>
-      </c>
-      <c r="AP31" s="1" t="inlineStr">
-        <is>
-          <t>TS%</t>
-        </is>
-      </c>
-      <c r="AQ31" s="1" t="inlineStr">
-        <is>
-          <t>PTS/PLAY</t>
-        </is>
-      </c>
-      <c r="AR31" s="1" t="inlineStr">
-        <is>
-          <t>TO%</t>
-        </is>
-      </c>
-      <c r="AS31" s="1" t="inlineStr">
-        <is>
-          <t>FTR</t>
-        </is>
-      </c>
-      <c r="AT31" s="1" t="inlineStr">
-        <is>
-          <t>Ass/TO</t>
-        </is>
-      </c>
-      <c r="AU31" s="1" t="inlineStr">
-        <is>
-          <t>Sh/TO</t>
-        </is>
-      </c>
-      <c r="AV31" s="1" t="inlineStr">
-        <is>
-          <t>Gen/TO</t>
-        </is>
-      </c>
-      <c r="AW31" s="1" t="inlineStr">
-        <is>
-          <t>USG%</t>
-        </is>
-      </c>
-      <c r="AX31" s="1" t="inlineStr">
-        <is>
-          <t>OR%</t>
-        </is>
-      </c>
-      <c r="AY31" s="1" t="inlineStr">
-        <is>
-          <t>DR%</t>
-        </is>
-      </c>
-      <c r="AZ31" s="1" t="inlineStr">
-        <is>
-          <t>pAST%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>#1 K. TAYLOR</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3</v>
-      </c>
-      <c r="P32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>61:22</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" t="n">
+        <v>26</v>
+      </c>
+      <c r="K30" t="n">
         <v>9</v>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="AV32" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>6.2%</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>5.1%</t>
+      <c r="L30" t="n">
+        <v>5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>19</v>
+      </c>
+      <c r="R30" t="n">
+        <v>21</v>
+      </c>
+      <c r="S30" t="n">
+        <v>84</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>77.4%</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>84.04000000000001</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>49.2%</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>56.5%</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>#2 J. PUERTO</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>18:39</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>25.3%</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AV33" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>22.3%</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>11.0%</t>
-        </is>
-      </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+          <t>VALENCIA BASKET</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>#3 N. REUVERS</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>13</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6</v>
-      </c>
-      <c r="S34" t="n">
-        <v>18</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>50:47</t>
-        </is>
-      </c>
-      <c r="AN34" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>61.1%</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>8.8%</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>JUGADOR</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>2PM</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>2PA</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>3PM</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>3PA</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>FTM</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>FTA</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>DRB</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>ORB</t>
+        </is>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>BLK A.</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>TO</t>
+        </is>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>TOunf</t>
+        </is>
+      </c>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="R34" s="1" t="inlineStr">
+        <is>
+          <t>F+</t>
+        </is>
+      </c>
+      <c r="S34" s="1" t="inlineStr">
+        <is>
+          <t>EFI</t>
+        </is>
+      </c>
+      <c r="T34" s="1" t="inlineStr">
+        <is>
+          <t>TOpts</t>
+        </is>
+      </c>
+      <c r="U34" s="1" t="inlineStr">
+        <is>
+          <t>2CPts</t>
+        </is>
+      </c>
+      <c r="V34" s="1" t="inlineStr">
+        <is>
+          <t>FastBPts</t>
+        </is>
+      </c>
+      <c r="W34" s="1" t="inlineStr">
+        <is>
+          <t>FastB Opp</t>
+        </is>
+      </c>
+      <c r="X34" s="1" t="inlineStr">
+        <is>
+          <t>Rim FGM</t>
+        </is>
+      </c>
+      <c r="Y34" s="1" t="inlineStr">
+        <is>
+          <t>Rim FGA</t>
+        </is>
+      </c>
+      <c r="Z34" s="1" t="inlineStr">
+        <is>
+          <t>Rim %</t>
+        </is>
+      </c>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t>Paint FGM</t>
+        </is>
+      </c>
+      <c r="AB34" s="1" t="inlineStr">
+        <is>
+          <t>Paint FGA</t>
+        </is>
+      </c>
+      <c r="AC34" s="1" t="inlineStr">
+        <is>
+          <t>Paint %</t>
+        </is>
+      </c>
+      <c r="AD34" s="1" t="inlineStr">
+        <is>
+          <t>MR FGM</t>
+        </is>
+      </c>
+      <c r="AE34" s="1" t="inlineStr">
+        <is>
+          <t>MR FGA</t>
+        </is>
+      </c>
+      <c r="AF34" s="1" t="inlineStr">
+        <is>
+          <t>MR %</t>
+        </is>
+      </c>
+      <c r="AG34" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 FGM</t>
+        </is>
+      </c>
+      <c r="AH34" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 FGA</t>
+        </is>
+      </c>
+      <c r="AI34" s="1" t="inlineStr">
+        <is>
+          <t>Cor3 %</t>
+        </is>
+      </c>
+      <c r="AJ34" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 FGM</t>
+        </is>
+      </c>
+      <c r="AK34" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 FGA</t>
+        </is>
+      </c>
+      <c r="AL34" s="1" t="inlineStr">
+        <is>
+          <t>ATB3 %</t>
+        </is>
+      </c>
+      <c r="AM34" s="1" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="AN34" s="1" t="inlineStr">
+        <is>
+          <t>PLAYS</t>
+        </is>
+      </c>
+      <c r="AO34" s="1" t="inlineStr">
+        <is>
+          <t>eFG%</t>
+        </is>
+      </c>
+      <c r="AP34" s="1" t="inlineStr">
+        <is>
+          <t>TS%</t>
+        </is>
+      </c>
+      <c r="AQ34" s="1" t="inlineStr">
+        <is>
+          <t>PTS/PLAY</t>
+        </is>
+      </c>
+      <c r="AR34" s="1" t="inlineStr">
+        <is>
+          <t>TO%</t>
+        </is>
+      </c>
+      <c r="AS34" s="1" t="inlineStr">
+        <is>
+          <t>FTR</t>
+        </is>
+      </c>
+      <c r="AT34" s="1" t="inlineStr">
+        <is>
+          <t>Ass/TO</t>
+        </is>
+      </c>
+      <c r="AU34" s="1" t="inlineStr">
+        <is>
+          <t>Sh/TO</t>
+        </is>
+      </c>
+      <c r="AV34" s="1" t="inlineStr">
+        <is>
+          <t>Gen/TO</t>
+        </is>
+      </c>
+      <c r="AW34" s="1" t="inlineStr">
+        <is>
+          <t>USG%</t>
+        </is>
+      </c>
+      <c r="AX34" s="1" t="inlineStr">
+        <is>
+          <t>OR%</t>
+        </is>
+      </c>
+      <c r="AY34" s="1" t="inlineStr">
+        <is>
+          <t>DR%</t>
+        </is>
+      </c>
+      <c r="AZ34" s="1" t="inlineStr">
+        <is>
+          <t>pAST%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>#4 J. PRADILLA</t>
+          <t>#1 K. TAYLOR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4850,34 +4262,34 @@
         <v>2</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>3</v>
       </c>
-      <c r="K35" t="n">
+      <c r="P35" t="n">
         <v>3</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4886,60 +4298,60 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AJ35" t="n">
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
@@ -4948,161 +4360,161 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>41:59</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="AN35" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr">
+        <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>#5 S. DE LARREA</t>
+          <t>#2 J. PUERTO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2</v>
       </c>
       <c r="Y36" t="n">
         <v>4</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -5110,21 +4522,21 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -5135,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -5144,81 +4556,81 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>44:54</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AN36" t="n">
-        <v>8.879999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>#10 O. MOORE</t>
+          <t>#3 N. REUVERS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -5233,49 +4645,49 @@
         <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -5284,21 +4696,21 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y37" t="n">
         <v>5</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -5317,137 +4729,137 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AJ37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>57:09</t>
-        </is>
-      </c>
-      <c r="AN37" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>61.5%</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>#12 N. SAKO</t>
+          <t>#4 J. PRADILLA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
         <v>3</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -5459,107 +4871,107 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>11</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AN38" t="n">
         <v>3</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>-4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>05:42</t>
-        </is>
-      </c>
-      <c r="AN38" t="n">
-        <v>4</v>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -5569,143 +4981,143 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>#13 D. THOMPSON</t>
+          <t>#5 S. DE LARREA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
         <v>6</v>
       </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="n">
         <v>4</v>
       </c>
-      <c r="G39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>15</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>3</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>6</v>
-      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AG39" t="n">
@@ -5720,23 +5132,23 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>32:22</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AN39" t="n">
-        <v>13.32</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -5745,80 +5157,80 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>#18 I. IROEGBU</t>
+          <t>#10 O. MOORE</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>3</v>
@@ -5827,429 +5239,429 @@
         <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK40" t="n">
         <v>4</v>
       </c>
-      <c r="W40" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1</v>
-      </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>27:10</t>
         </is>
       </c>
       <c r="AN40" t="n">
-        <v>3.76</v>
+        <v>11.76</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>150.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>#24 M. COSTELLO</t>
+          <t>#12 N. SAKO</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="AN41" t="n">
         <v>4</v>
       </c>
-      <c r="D41" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>19</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>4</v>
-      </c>
-      <c r="V41" t="n">
-        <v>2</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2</v>
-      </c>
-      <c r="X41" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>85.7%</t>
-        </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>27:03</t>
-        </is>
-      </c>
-      <c r="AN41" t="n">
-        <v>9.880000000000001</v>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>#32 I. NOGUES</t>
+          <t>#13 D. THOMPSON</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -6264,25 +5676,25 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AD42" t="n">
@@ -6308,120 +5720,120 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>02:02</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AN42" t="n">
-        <v>1</v>
+        <v>13.32</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>#77 N. SESTINA</t>
+          <t>#18 I. IROEGBU</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>8</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
         <v>3</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -6442,16 +5854,16 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6460,21 +5872,21 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -6493,48 +5905,48 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>33:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AN43" t="n">
-        <v>9</v>
+        <v>3.76</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
@@ -6544,7 +5956,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>150.0%</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
@@ -6564,603 +5976,1191 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>#24 M. COSTELLO</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>13</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
       <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>19</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="n">
-        <v>3</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr"/>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>9.880000000000001</v>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>#32 I. NOGUES</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>20.7%</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>#77 N. SESTINA</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B48" t="n">
         <v>80</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C48" t="n">
         <v>14</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D48" t="n">
         <v>35</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E48" t="n">
         <v>12</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F48" t="n">
         <v>35</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G48" t="n">
         <v>16</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H48" t="n">
         <v>23</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I48" t="n">
         <v>21</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J48" t="n">
         <v>30</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K48" t="n">
         <v>20</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L48" t="n">
         <v>6</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M48" t="n">
         <v>4</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>15</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P48" t="n">
         <v>14</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q48" t="n">
         <v>16</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R48" t="n">
         <v>22</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S48" t="n">
         <v>101</v>
       </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
-        <v>21</v>
-      </c>
-      <c r="V45" t="n">
-        <v>12</v>
-      </c>
-      <c r="W45" t="n">
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>68.3%</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" t="n">
         <v>8</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK48" t="n">
         <v>28</v>
       </c>
-      <c r="Y45" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>68.3%</t>
-        </is>
-      </c>
-      <c r="AA45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="AD45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>9</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL48" t="inlineStr">
         <is>
           <t>32.1%</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM48" t="inlineStr">
         <is>
           <t>200:00</t>
         </is>
       </c>
-      <c r="AN45" t="n">
+      <c r="AN48" t="n">
         <v>95.12</v>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>45.7%</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr">
+      <c r="AP48" t="inlineStr">
         <is>
           <t>49.9%</t>
         </is>
       </c>
-      <c r="AQ45" t="inlineStr">
+      <c r="AQ48" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AR48" t="inlineStr">
         <is>
           <t>15.8%</t>
         </is>
       </c>
-      <c r="AS45" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>22.9%</t>
         </is>
       </c>
-      <c r="AT45" t="inlineStr">
+      <c r="AT48" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="AU45" t="inlineStr">
+      <c r="AU48" t="inlineStr">
         <is>
           <t>4.67</t>
         </is>
       </c>
-      <c r="AV45" t="inlineStr">
+      <c r="AV48" t="inlineStr">
         <is>
           <t>6.07</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr">
+      <c r="AY48" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>80.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>--- Glossary of Terms ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>Explanation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>EFI</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Efficiency Rating (Official ACB/FEB Formula): (PTS + REB + AST + STL + BLK + F+) - (FGA-FGM + FTA-FTM + TO + BLK A. + F)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BLK A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Blocks Against: A player's shot attempt was blocked by an opponent.</t>
+          <t>--- Glossary of Terms ---</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>F+</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Fouls Received: The number of times a player was fouled by an opponent.</t>
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TOunf</t>
+          <t>EFI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Unforced Turnovers: Turnovers not resulting from a direct steal (e.g., bad pass, out of bounds).</t>
+          <t>Efficiency Rating (Official ACB/FEB Formula): (PTS + REB + AST + STL + BLK + F+) - (FGA-FGM + FTA-FTM + TO + BLK A. + F)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2CPts</t>
+          <t>BLK A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2nd Chance Points: Points scored within 8 seconds immediately following an offensive rebound.</t>
+          <t>Blocks Against: A player's shot attempt was blocked by an opponent.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TOpts</t>
+          <t>F+</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Points off Turnovers: Points scored on any possession that was initiated by an opponent's turnover (possession-based).</t>
+          <t>Fouls Received: The number of times a player was fouled by an opponent.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FastBPts</t>
+          <t>TOunf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fast Break Points: Points scored by a player on a fast break. Includes points from FTs after a foul.</t>
+          <t>Unforced Turnovers: Turnovers not resulting from a direct steal (e.g., bad pass, out of bounds).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FastB Opp</t>
+          <t>2CPts</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fast Break Opportunity: When a player scores a FG or is fouled on a fast break. A fast break is a play within 8 seconds of a DRB, STL, or opponent's made basket.</t>
+          <t>2nd Chance Points: Points scored within 8 seconds immediately following an offensive rebound.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PLAYS</t>
+          <t>TOpts</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>An estimate of possessions used by a player. Formula: FGA + (0.44 * FTA) + TO</t>
+          <t>Points off Turnovers: Points scored on any possession that was initiated by an opponent's turnover (possession-based).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>eFG%</t>
+          <t>FastBPts</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Effective Field Goal Percentage. Adjusts for the fact that a 3-point field goal is worth more than a 2-point field goal.</t>
+          <t>Fast Break Points: Points scored by a player on a fast break. Includes points from FTs after a foul.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TS%</t>
+          <t>FastB Opp</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>True Shooting Percentage. Measures shooting efficiency, taking into account 2-pt, 3-pt, and free throws.</t>
+          <t>Fast Break Opportunity: When a player scores a FG or is fouled on a fast break. A fast break is a play within 8 seconds of a DRB, STL, or opponent's made basket.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TO%</t>
+          <t>PLAYS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Turnover Percentage. An estimate of turnovers per 100 plays.</t>
+          <t>An estimate of possessions used by a player. Formula: FGA + (0.44 * FTA) + TO</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FTR</t>
+          <t>eFG%</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Free Throw Rate. How frequently a player scores from the free throw line relative to their field goal attempts.</t>
+          <t>Effective Field Goal Percentage. Adjusts for the fact that a 3-point field goal is worth more than a 2-point field goal.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ass/TO</t>
+          <t>TS%</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Assist to Turnover Ratio. A measure of a player's ball security and playmaking.</t>
+          <t>True Shooting Percentage. Measures shooting efficiency, taking into account 2-pt, 3-pt, and free throws.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sh/TO</t>
+          <t>TO%</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shot to Turnover Ratio. The number of field goal attempts a player takes for every turnover they commit.</t>
+          <t>Turnover Percentage. An estimate of turnovers per 100 plays.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gen/TO</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Generated Offense to Turnover Ratio. The number of shots and assists a player generates for every turnover.</t>
+          <t>Free Throw Rate. How frequently a player scores from the free throw line relative to their field goal attempts.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>USG%</t>
+          <t>Ass/TO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Usage Rate. An estimate of the percentage of a team's offensive possessions a player 'uses' while on the floor.</t>
+          <t>Assist to Turnover Ratio. A measure of a player's ball security and playmaking.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OR% / DR%</t>
+          <t>Sh/TO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Offensive/Defensive Rebound Percentage. Percentage of available offensive/defensive rebounds a player secured while on the floor.</t>
+          <t>Shot to Turnover Ratio. The number of field goal attempts a player takes for every turnover they commit.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Gen/TO</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Generated Offense to Turnover Ratio. The number of shots and assists a player generates for every turnover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>USG%</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Usage Rate. An estimate of the percentage of a team's offensive possessions a player 'uses' while on the floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>OR% / DR%</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Offensive/Defensive Rebound Percentage. Percentage of available offensive/defensive rebounds a player secured while on the floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>pAST%</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Assist Percentage. An estimate of the percentage of teammate field goals a player assisted on while on the floor.</t>
         </is>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>22</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2903,10 +2903,10 @@
         <v>10</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,10 +3099,10 @@
         <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>15</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3827,16 +3827,16 @@
         <v>84</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4488,16 +4488,16 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>3</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5076,10 +5076,10 @@
         <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5667,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>5</v>
@@ -5863,13 +5863,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" t="n">
         <v>4</v>
@@ -6059,13 +6059,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X44" t="n">
         <v>6</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>101</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_10_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -854,17 +854,17 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
         <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>68.29</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" t="n">
         <v>3</v>
       </c>
-      <c r="Y36" t="n">
-        <v>4</v>
-      </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5676,14 +5676,14 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,10 +5872,10 @@
         <v>2</v>
       </c>
       <c r="X43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>2</v>
       </c>
       <c r="X44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6496,18 +6496,18 @@
         <v>1</v>
       </c>
       <c r="AH46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
         <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>3</v>
       </c>
       <c r="AH48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>9</v>
       </c>
       <c r="AK48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
